--- a/tools/importer/reports/import-individual-plan-page.report.xlsx
+++ b/tools/importer/reports/import-individual-plan-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>individual-plan-page</t>
   </si>
   <si>
-    <t>2026-03-16T16:32:31.044Z</t>
+    <t>2026-03-16T21:32:47.267Z</t>
   </si>
   <si>
     <t>Blue Choice®—Personal plans | Alberta Blue Cross®</t>
